--- a/demo_data/sectors/uretim_sanayi/ap_aging.xlsx
+++ b/demo_data/sectors/uretim_sanayi/ap_aging.xlsx
@@ -474,7 +474,7 @@
         <v>46047</v>
       </c>
       <c r="D2" t="n">
-        <v>638446.03</v>
+        <v>622874.17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         <v>46059</v>
       </c>
       <c r="D3" t="n">
-        <v>532038.36</v>
+        <v>519061.81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         <v>46017</v>
       </c>
       <c r="D4" t="n">
-        <v>425630.68</v>
+        <v>415249.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         <v>46070</v>
       </c>
       <c r="D5" t="n">
-        <v>186213.42</v>
+        <v>181671.64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         <v>46064</v>
       </c>
       <c r="D6" t="n">
-        <v>186213.42</v>
+        <v>181671.63</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         <v>46042</v>
       </c>
       <c r="D7" t="n">
-        <v>319223.01</v>
+        <v>311437.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         <v>46082</v>
       </c>
       <c r="D8" t="n">
-        <v>319223.01</v>
+        <v>311437.09</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>46026</v>
       </c>
       <c r="D9" t="n">
-        <v>133009.59</v>
+        <v>129765.46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>46016</v>
       </c>
       <c r="D10" t="n">
-        <v>133009.59</v>
+        <v>129765.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>46046</v>
       </c>
       <c r="D11" t="n">
-        <v>133009.59</v>
+        <v>129765.46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>46049</v>
       </c>
       <c r="D12" t="n">
-        <v>133009.59</v>
+        <v>129765.45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46060</v>
       </c>
       <c r="D13" t="n">
-        <v>133009.59</v>
+        <v>129765.46</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>46059</v>
       </c>
       <c r="D14" t="n">
-        <v>133009.59</v>
+        <v>129765.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>46009</v>
       </c>
       <c r="D15" t="n">
-        <v>106407.67</v>
+        <v>103812.36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>46006</v>
       </c>
       <c r="D16" t="n">
-        <v>106407.67</v>
+        <v>103812.36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46029</v>
       </c>
       <c r="D17" t="n">
-        <v>106407.67</v>
+        <v>103812.36</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46028</v>
       </c>
       <c r="D18" t="n">
-        <v>106407.67</v>
+        <v>103812.36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46061</v>
       </c>
       <c r="D19" t="n">
-        <v>212815.34</v>
+        <v>207624.72</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>46010</v>
       </c>
       <c r="D20" t="n">
-        <v>186213.42</v>
+        <v>181671.63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46089</v>
       </c>
       <c r="D21" t="n">
-        <v>186213.42</v>
+        <v>181671.63</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46046</v>
       </c>
       <c r="D22" t="n">
-        <v>79805.75</v>
+        <v>77859.27</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46040</v>
       </c>
       <c r="D23" t="n">
-        <v>79805.75</v>
+        <v>77859.27</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46010</v>
       </c>
       <c r="D24" t="n">
-        <v>159611.51</v>
+        <v>155718.54</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46047</v>
       </c>
       <c r="D25" t="n">
-        <v>66504.78999999999</v>
+        <v>64882.72</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>46040</v>
       </c>
       <c r="D26" t="n">
-        <v>66504.78999999999</v>
+        <v>64882.73</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46065</v>
       </c>
       <c r="D27" t="n">
-        <v>66504.78999999999</v>
+        <v>64882.72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>46057</v>
       </c>
       <c r="D28" t="n">
-        <v>66504.78999999999</v>
+        <v>64882.73</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>46062</v>
       </c>
       <c r="D29" t="n">
-        <v>53203.84</v>
+        <v>51906.18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>46070</v>
       </c>
       <c r="D30" t="n">
-        <v>53203.84</v>
+        <v>51906.18</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46015</v>
       </c>
       <c r="D31" t="n">
-        <v>106407.67</v>
+        <v>103812.36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>46033</v>
       </c>
       <c r="D32" t="n">
-        <v>39902.88</v>
+        <v>38929.64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>46031</v>
       </c>
       <c r="D33" t="n">
-        <v>39902.88</v>
+        <v>38929.63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46047</v>
       </c>
       <c r="D34" t="n">
-        <v>39902.88</v>
+        <v>38929.64</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46042</v>
       </c>
       <c r="D35" t="n">
-        <v>39902.88</v>
+        <v>38929.63</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>46062</v>
       </c>
       <c r="D36" t="n">
-        <v>39902.88</v>
+        <v>38929.64</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>46047</v>
       </c>
       <c r="D37" t="n">
-        <v>39902.88</v>
+        <v>38929.65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>

--- a/demo_data/sectors/uretim_sanayi/ap_aging.xlsx
+++ b/demo_data/sectors/uretim_sanayi/ap_aging.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="D2" t="n">
-        <v>622874.17</v>
+        <v>443365.29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Erdemir Ereğli Demir ve Çelik A.Ş.</t>
+          <t>İsdemir İskenderun Demir Çelik A.Ş.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46059</v>
+        <v>46038</v>
       </c>
       <c r="D3" t="n">
-        <v>519061.81</v>
+        <v>443365.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tosyalı Çelik Profil Sanayi A.Ş.</t>
+          <t>Erdemir Ereğli Demir ve Çelik A.Ş.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46017</v>
+        <v>46055</v>
       </c>
       <c r="D4" t="n">
-        <v>415249.45</v>
+        <v>387944.64</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kordsa Teknik Tekstil A.Ş.</t>
+          <t>Erdemir Ereğli Demir ve Çelik A.Ş.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46070</v>
+        <v>46064</v>
       </c>
       <c r="D5" t="n">
-        <v>181671.64</v>
+        <v>387944.63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kordsa Teknik Tekstil A.Ş.</t>
+          <t>Tosyalı Çelik Profil Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46064</v>
+        <v>46016</v>
       </c>
       <c r="D6" t="n">
-        <v>181671.63</v>
+        <v>554206.62</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aksa Akrilik Kimya Sanayii A.Ş.</t>
+          <t>Kordsa Teknik Tekstil A.Ş.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46042</v>
+        <v>46068</v>
       </c>
       <c r="D7" t="n">
-        <v>311437.09</v>
+        <v>221682.65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sasa Polyester Sanayi A.Ş.</t>
+          <t>Kordsa Teknik Tekstil A.Ş.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46082</v>
+        <v>46064</v>
       </c>
       <c r="D8" t="n">
-        <v>311437.09</v>
+        <v>221682.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Toros Tarım Sanayi ve Ticaret</t>
+          <t>Sarkuysan Elektrolitik Bakır Sanayi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46026</v>
+        <v>46084</v>
       </c>
       <c r="D9" t="n">
-        <v>129765.46</v>
+        <v>443365.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Toros Tarım Sanayi ve Ticaret</t>
+          <t>Borusan Mannesmann Boru A.Ş.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46016</v>
+        <v>45999</v>
       </c>
       <c r="D10" t="n">
-        <v>129765.45</v>
+        <v>221682.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gentaş Kimya Sanayi Pazarlama</t>
+          <t>Borusan Mannesmann Boru A.Ş.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46046</v>
+        <v>46004</v>
       </c>
       <c r="D11" t="n">
-        <v>129765.46</v>
+        <v>221682.65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gentaş Kimya Sanayi Pazarlama</t>
+          <t>Alkim Alkali Kimya A.Ş.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="D12" t="n">
-        <v>129765.45</v>
+        <v>332523.97</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alkim Alkali Kimya A.Ş.</t>
+          <t>Gentaş Kimya Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46060</v>
+        <v>46056</v>
       </c>
       <c r="D13" t="n">
-        <v>129765.46</v>
+        <v>166261.98</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alkim Alkali Kimya A.Ş.</t>
+          <t>Gentaş Kimya Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46059</v>
+        <v>46053</v>
       </c>
       <c r="D14" t="n">
-        <v>129765.45</v>
+        <v>166261.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tat Gıda Sanayi A.Ş.</t>
+          <t>SKF Türk Sanayi ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46009</v>
+        <v>46068</v>
       </c>
       <c r="D15" t="n">
-        <v>103812.36</v>
+        <v>332523.97</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tat Gıda Sanayi A.Ş.</t>
+          <t>Bosch Rexroth Otomasyon Sanayi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46006</v>
+        <v>46038</v>
       </c>
       <c r="D16" t="n">
-        <v>103812.36</v>
+        <v>166261.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pınar Süt Mamülleri Sanayii A.Ş.</t>
+          <t>Bosch Rexroth Otomasyon Sanayi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46029</v>
+        <v>46040</v>
       </c>
       <c r="D17" t="n">
-        <v>103812.36</v>
+        <v>166261.99</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pınar Süt Mamülleri Sanayii A.Ş.</t>
+          <t>Castrol Madeni Yağlar Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46028</v>
+        <v>46017</v>
       </c>
       <c r="D18" t="n">
-        <v>103812.36</v>
+        <v>221682.65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Banvit Bandırma Vitaminli Yem</t>
+          <t>Ege Çelik Endüstrisi Sanayi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -862,426 +862,12 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46061</v>
+        <v>46072</v>
       </c>
       <c r="D19" t="n">
-        <v>207624.72</v>
+        <v>221682.65</v>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Borusan Mannesmann Boru A.Ş.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BL-2019</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="D20" t="n">
-        <v>181671.63</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sarkuysan Elektrolitik Bakır Sanayi</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BL-2020</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="D21" t="n">
-        <v>181671.63</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Kastamonu Entegre Ağaç Sanayi</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BL-2021</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>46046</v>
-      </c>
-      <c r="D22" t="n">
-        <v>77859.27</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Kastamonu Entegre Ağaç Sanayi</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BL-2022</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="D23" t="n">
-        <v>77859.27</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Yıldız Entegre Ağaç Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BL-2023</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="D24" t="n">
-        <v>155718.54</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Çamsan Ağaç Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BL-2024</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="D25" t="n">
-        <v>64882.72</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Çamsan Ağaç Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BL-2025</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="D26" t="n">
-        <v>64882.73</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Ege Seramik Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BL-2026</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="D27" t="n">
-        <v>64882.72</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Ege Seramik Sanayi ve Ticaret</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BL-2027</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>46057</v>
-      </c>
-      <c r="D28" t="n">
-        <v>64882.73</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Kütahya Porselen Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BL-2028</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="D29" t="n">
-        <v>51906.18</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Kütahya Porselen Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BL-2029</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="D30" t="n">
-        <v>51906.18</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Akzo Nobel Boya Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BL-2030</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="D31" t="n">
-        <v>103812.36</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DYO Boya Fabrikaları Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BL-2031</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>46033</v>
-      </c>
-      <c r="D32" t="n">
-        <v>38929.64</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DYO Boya Fabrikaları Sanayi A.Ş.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BL-2032</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="D33" t="n">
-        <v>38929.63</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Polisan Holding Kimya Sanayi</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BL-2033</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="D34" t="n">
-        <v>38929.64</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Polisan Holding Kimya Sanayi</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BL-2034</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>46042</v>
-      </c>
-      <c r="D35" t="n">
-        <v>38929.63</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Filli Boya Betek Boya ve Kimya</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BL-2035</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="D36" t="n">
-        <v>38929.64</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Filli Boya Betek Boya ve Kimya</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BL-2036</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>46047</v>
-      </c>
-      <c r="D37" t="n">
-        <v>38929.65</v>
-      </c>
-      <c r="E37" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
